--- a/Loan-default-analysis-dashboard.xlsx
+++ b/Loan-default-analysis-dashboard.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\enuod\Desktop\Loan_Default_Risk Analysis_Project\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{C1F4DC82-EF88-4F3F-BAC2-6D5995006BA9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{84A58104-0F91-40FD-8469-B6C6B15DCDB7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13176" xr2:uid="{D499663C-E28D-4ACB-88B3-018D67624079}"/>
+    <workbookView xWindow="0" yWindow="12" windowWidth="23256" windowHeight="13176" xr2:uid="{D499663C-E28D-4ACB-88B3-018D67624079}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -7404,7 +7404,7 @@
       <xdr:row>12</xdr:row>
       <xdr:rowOff>114300</xdr:rowOff>
     </xdr:to>
-    <xdr:sp macro="" textlink="[1]dashboard!C5">
+    <xdr:sp macro="" textlink="#REF!">
       <xdr:nvSpPr>
         <xdr:cNvPr id="14" name="TextBox 13">
           <a:extLst>
@@ -7489,7 +7489,7 @@
       <xdr:row>18</xdr:row>
       <xdr:rowOff>83820</xdr:rowOff>
     </xdr:to>
-    <xdr:sp macro="" textlink="[1]dashboard!C9">
+    <xdr:sp macro="" textlink="#REF!">
       <xdr:nvSpPr>
         <xdr:cNvPr id="15" name="TextBox 14">
           <a:extLst>
@@ -7785,7 +7785,7 @@
       <xdr:row>24</xdr:row>
       <xdr:rowOff>83820</xdr:rowOff>
     </xdr:to>
-    <xdr:sp macro="" textlink="[1]dashboard!C12">
+    <xdr:sp macro="" textlink="#REF!">
       <xdr:nvSpPr>
         <xdr:cNvPr id="20" name="TextBox 19">
           <a:extLst>
@@ -8801,21 +8801,19 @@
       <sheetName val="default rate by credit score ba"/>
       <sheetName val="high risk combined segment"/>
       <sheetName val="interesr rate vs default"/>
-      <sheetName val="dashboard"/>
       <sheetName val="Sheet1"/>
     </sheetNames>
     <sheetDataSet>
-      <sheetData sheetId="0"/>
-      <sheetData sheetId="1"/>
-      <sheetData sheetId="2"/>
-      <sheetData sheetId="3"/>
-      <sheetData sheetId="4"/>
-      <sheetData sheetId="5"/>
-      <sheetData sheetId="6"/>
-      <sheetData sheetId="7"/>
-      <sheetData sheetId="8"/>
-      <sheetData sheetId="9"/>
-      <sheetData sheetId="10"/>
+      <sheetData sheetId="0" refreshError="1"/>
+      <sheetData sheetId="1" refreshError="1"/>
+      <sheetData sheetId="2" refreshError="1"/>
+      <sheetData sheetId="3" refreshError="1"/>
+      <sheetData sheetId="4" refreshError="1"/>
+      <sheetData sheetId="5" refreshError="1"/>
+      <sheetData sheetId="6" refreshError="1"/>
+      <sheetData sheetId="7" refreshError="1"/>
+      <sheetData sheetId="8" refreshError="1"/>
+      <sheetData sheetId="9" refreshError="1"/>
     </sheetDataSet>
   </externalBook>
 </externalLink>
